--- a/YSIG/Stock Pitch/VICI/10q/VICI Over Time.xlsx
+++ b/YSIG/Stock Pitch/VICI/10q/VICI Over Time.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Documents/Notes/YSIG/Stock Pitch/VICI/10q/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4C973D-B938-2447-BF50-FF3761FAF1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6210C1-22AC-CE49-BB85-1B4ABB857129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" xr2:uid="{E4D61E25-3F2C-2549-A6B3-A831DB9DF31D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" activeTab="2" xr2:uid="{E4D61E25-3F2C-2549-A6B3-A831DB9DF31D}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="DCF Calculations" sheetId="2" r:id="rId2"/>
     <sheet name="DCF Calculations (Continued)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -433,33 +433,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -895,54 +889,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582EA3D0-48F1-6C46-B799-25505063D899}">
-  <dimension ref="A1:U60"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="53.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="5"/>
-    <col min="6" max="6" width="10.83203125" style="5"/>
-    <col min="8" max="8" width="10.83203125" style="5"/>
-    <col min="10" max="10" width="10.83203125" style="5"/>
-    <col min="12" max="12" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -958,7 +947,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
-      <c r="N2" s="8"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
@@ -967,35 +956,35 @@
       <c r="C3" s="1">
         <v>22985837</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f>(E3-C3)/C3*100</f>
         <v>0.88632404380140695</v>
       </c>
       <c r="E3" s="1">
         <v>23189566</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <f>(G3-E3)/E3*100</f>
         <v>1.0356640568434958</v>
       </c>
       <c r="G3" s="1">
         <v>23429732</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <f>(I3-G3)/G3*100</f>
         <v>0.64605519175379378</v>
       </c>
       <c r="I3" s="1">
         <v>23581101</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <f>(K3-I3)/I3*100</f>
         <v>-0.31562139528599614</v>
       </c>
       <c r="K3" s="1">
         <v>23506674</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <f>(M3-K3)/K3*100</f>
         <v>0.76681201262245779</v>
       </c>
@@ -1011,35 +1000,35 @@
       <c r="C4" s="1">
         <v>18266712</v>
       </c>
-      <c r="D4" s="7">
-        <f t="shared" ref="D4:F7" si="0">(E4-C4)/C4*100</f>
+      <c r="D4" s="5">
+        <f t="shared" ref="D4:D7" si="0">(E4-C4)/C4*100</f>
         <v>0.38961034695242358</v>
       </c>
       <c r="E4" s="1">
         <v>18337881</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <f t="shared" ref="F4" si="1">(G4-E4)/E4*100</f>
         <v>0.39385139428050597</v>
       </c>
       <c r="G4" s="1">
         <v>18410105</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <f t="shared" ref="H4" si="2">(I4-G4)/G4*100</f>
         <v>0.10980382784345881</v>
       </c>
       <c r="I4" s="1">
         <v>18430320</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <f t="shared" ref="J4" si="3">(K4-I4)/I4*100</f>
         <v>0.1340020140724632</v>
       </c>
       <c r="K4" s="1">
         <v>18455017</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <f t="shared" ref="L4" si="4">(M4-K4)/K4*100</f>
         <v>0.66413918773415381</v>
       </c>
@@ -1055,35 +1044,35 @@
       <c r="C5" s="1">
         <v>1224987</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>19.282735245353624</v>
       </c>
       <c r="E5" s="1">
         <v>1461198</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <f t="shared" ref="F5" si="5">(G5-E5)/E5*100</f>
         <v>6.1238791731168538</v>
       </c>
       <c r="G5" s="1">
         <v>1550680</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <f t="shared" ref="H5" si="6">(I5-G5)/G5*100</f>
         <v>6.503791884850517</v>
       </c>
       <c r="I5" s="1">
         <v>1651533</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <f t="shared" ref="J5" si="7">(K5-I5)/I5*100</f>
         <v>23.31167466832331</v>
       </c>
       <c r="K5" s="1">
         <v>2036533</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <f t="shared" ref="L5" si="8">(M5-K5)/K5*100</f>
         <v>16.327552757554137</v>
       </c>
@@ -1099,35 +1088,35 @@
       <c r="C6" s="1">
         <v>150727</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>150727</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <f t="shared" ref="F6" si="9">(G6-E6)/E6*100</f>
         <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>150727</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <f t="shared" ref="H6" si="10">(I6-G6)/G6*100</f>
         <v>0</v>
       </c>
       <c r="I6" s="1">
         <v>150727</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <f t="shared" ref="J6" si="11">(K6-I6)/I6*100</f>
         <v>0</v>
       </c>
       <c r="K6" s="1">
         <v>150727</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <f t="shared" ref="L6" si="12">(M6-K6)/K6*100</f>
         <v>-0.62364407173233727</v>
       </c>
@@ -1143,35 +1132,35 @@
       <c r="C7" s="1">
         <v>44157873</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>0.8002582008422372</v>
       </c>
       <c r="E7" s="1">
         <v>44511250</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <f t="shared" ref="F7" si="13">(G7-E7)/E7*100</f>
         <v>0.91405206548906182</v>
       </c>
       <c r="G7" s="1">
         <v>44918106</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <f t="shared" ref="H7" si="14">(I7-G7)/G7*100</f>
         <v>1.0036798969217446</v>
       </c>
       <c r="I7" s="1">
         <v>45368940</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <f t="shared" ref="J7" si="15">(K7-I7)/I7*100</f>
         <v>0.34632504087598259</v>
       </c>
       <c r="K7" s="1">
         <v>45526064</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <f t="shared" ref="L7" si="16">(M7-K7)/K7*100</f>
         <v>0.96955669174475534</v>
       </c>
@@ -1181,15 +1170,15 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="D8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="L8" s="5"/>
       <c r="M8" s="1"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1205,7 +1194,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="8"/>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
@@ -1214,35 +1203,35 @@
       <c r="C10" s="1">
         <v>16711739</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <f>(E10-C10)/C10*100</f>
         <v>9.3479200459030631E-2</v>
       </c>
       <c r="E10" s="1">
         <v>16727361</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <f>(G10-E10)/E10*100</f>
         <v>9.6984814281224629E-2</v>
       </c>
       <c r="G10" s="1">
         <v>16743584</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <f>(I10-G10)/G10*100</f>
         <v>-6.3875213335448378E-2</v>
       </c>
       <c r="I10" s="1">
         <v>16732889</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <f>(K10-I10)/I10*100</f>
         <v>0.68196233178861099</v>
       </c>
       <c r="K10" s="1">
         <v>16847001</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <f>(M10-K10)/K10*100</f>
         <v>0.4467976229122323</v>
       </c>
@@ -1258,35 +1247,35 @@
       <c r="C11" s="1">
         <v>186556</v>
       </c>
-      <c r="D11" s="7">
-        <f t="shared" ref="D11:D35" si="17">(E11-C11)/C11*100</f>
+      <c r="D11" s="5">
+        <f t="shared" ref="D11:D13" si="17">(E11-C11)/C11*100</f>
         <v>15.616222474752888</v>
       </c>
       <c r="E11" s="1">
         <v>215689</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <f t="shared" ref="F11" si="18">(G11-E11)/E11*100</f>
         <v>-9.9624922921428531</v>
       </c>
       <c r="G11" s="1">
         <v>194201</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <f t="shared" ref="H11" si="19">(I11-G11)/G11*100</f>
         <v>12.232171821978259</v>
       </c>
       <c r="I11" s="1">
         <v>217956</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <f t="shared" ref="J11" si="20">(K11-I11)/I11*100</f>
         <v>-12.116206940850446</v>
       </c>
       <c r="K11" s="1">
         <v>191548</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <f t="shared" ref="L11" si="21">(M11-K11)/K11*100</f>
         <v>14.756614530039469</v>
       </c>
@@ -1302,35 +1291,35 @@
       <c r="C12" s="1">
         <v>437766</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f t="shared" si="17"/>
         <v>4.34021829013674E-3</v>
       </c>
       <c r="E12" s="1">
         <v>437785</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <f t="shared" ref="F12" si="22">(G12-E12)/E12*100</f>
         <v>4.6123096953984266</v>
       </c>
       <c r="G12" s="1">
         <v>457977</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <f t="shared" ref="H12" si="23">(I12-G12)/G12*100</f>
         <v>0.86838422016826178</v>
       </c>
       <c r="I12" s="1">
         <v>461954</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="5">
         <f t="shared" ref="J12" si="24">(K12-I12)/I12*100</f>
         <v>2.9873104248474953E-2</v>
       </c>
       <c r="K12" s="1">
         <v>462092</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <f t="shared" ref="L12" si="25">(M12-K12)/K12*100</f>
         <v>4.5445495702154549E-3</v>
       </c>
@@ -1346,35 +1335,35 @@
       <c r="C13" s="1">
         <v>1003254</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <f t="shared" si="17"/>
         <v>8.4524955793846834E-2</v>
       </c>
       <c r="E13" s="1">
         <v>1004102</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <f t="shared" ref="F13" si="26">(G13-E13)/E13*100</f>
         <v>-0.4810268279517419</v>
       </c>
       <c r="G13" s="1">
         <v>999272</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <f t="shared" ref="H13" si="27">(I13-G13)/G13*100</f>
         <v>0.50716921919157143</v>
       </c>
       <c r="I13" s="1">
         <v>1004340</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <f t="shared" ref="J13" si="28">(K13-I13)/I13*100</f>
         <v>-0.15751637891550671</v>
       </c>
       <c r="K13" s="1">
         <v>1002758</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="5">
         <f t="shared" ref="L13" si="29">(M13-K13)/K13*100</f>
         <v>0.29448780264031804</v>
       </c>
@@ -1390,35 +1379,35 @@
       <c r="C14" s="1">
         <v>18339315</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <f>(E14-C14)/C14*100</f>
         <v>0.24876610713104605</v>
       </c>
       <c r="E14" s="1">
         <v>18384937</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <f t="shared" ref="F14" si="30">(G14-E14)/E14*100</f>
         <v>5.4919959747482407E-2</v>
       </c>
       <c r="G14" s="1">
         <v>18395034</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <f t="shared" ref="H14" si="31">(I14-G14)/G14*100</f>
         <v>0.12016830194497058</v>
       </c>
       <c r="I14" s="1">
         <v>18417139</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="5">
         <f t="shared" ref="J14" si="32">(K14-I14)/I14*100</f>
         <v>0.46836807823408405</v>
       </c>
       <c r="K14" s="1">
         <v>18503399</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <f t="shared" ref="L14" si="33">(M14-K14)/K14*100</f>
         <v>0.49559002645946293</v>
       </c>
@@ -1428,13 +1417,13 @@
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
@@ -1458,21 +1447,21 @@
       <c r="C17" s="1">
         <v>512772</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <f>(E17-C17)/C17*100</f>
         <v>-9.4193910743956374E-2</v>
       </c>
       <c r="E17" s="1">
         <v>512289</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <f>(G17-E17)/E17*100</f>
         <v>1.249685236263125</v>
       </c>
       <c r="G17" s="1">
         <v>518691</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <f>(I17-G17)/G17*100</f>
         <v>1.1567580698334847</v>
       </c>
@@ -1480,14 +1469,14 @@
         <f>2068443-C17-E17-G17</f>
         <v>524691</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="5">
         <f>(K17-I17)/I17*100</f>
         <v>0.74577227358578668</v>
       </c>
       <c r="K17" s="1">
         <v>528604</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="5">
         <f>(M17-K17)/K17*100</f>
         <v>0.32992561539451082</v>
       </c>
@@ -1502,21 +1491,21 @@
       <c r="C18" s="1">
         <v>409301</v>
       </c>
-      <c r="D18" s="7">
-        <f t="shared" ref="D18:F20" si="34">(E18-C18)/C18*100</f>
+      <c r="D18" s="5">
+        <f t="shared" ref="D18:D20" si="34">(E18-C18)/C18*100</f>
         <v>1.0833103266300352</v>
       </c>
       <c r="E18" s="1">
         <v>413735</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <f t="shared" ref="F18" si="35">(G18-E18)/E18*100</f>
         <v>1.3003492573748898</v>
       </c>
       <c r="G18" s="1">
         <v>419115</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <f t="shared" ref="H18" si="36">(I18-G18)/G18*100</f>
         <v>0.38724455101821698</v>
       </c>
@@ -1524,14 +1513,14 @@
         <f>1662889-C18-E18-G18</f>
         <v>420738</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="5">
         <f>(K18-I18)/I18*100</f>
         <v>1.3647448055559517</v>
       </c>
       <c r="K18" s="1">
         <v>426480</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="5">
         <f>(M18-K18)/K18*100</f>
         <v>3.2311011067341959</v>
       </c>
@@ -1546,21 +1535,21 @@
       <c r="C19" s="1">
         <v>19312</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <f t="shared" si="34"/>
         <v>5.6959403479701735E-2</v>
       </c>
       <c r="E19" s="1">
         <v>19323</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <f t="shared" ref="F19" si="37">(G19-E19)/E19*100</f>
         <v>-4.1401438699994825E-2</v>
       </c>
       <c r="G19" s="1">
         <v>19315</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="5">
         <f t="shared" ref="H19" si="38">(I19-G19)/G19*100</f>
         <v>0.81283976184312701</v>
       </c>
@@ -1568,14 +1557,14 @@
         <f>77422-C19-E19-G19</f>
         <v>19472</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="5">
         <f>(K19-I19)/I19*100</f>
         <v>0.21055875102711585</v>
       </c>
       <c r="K19" s="1">
         <v>19513</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="5">
         <f>(M19-K19)/K19*100</f>
         <v>0.1178701378568134</v>
       </c>
@@ -1590,21 +1579,21 @@
       <c r="C20" s="1">
         <v>10096</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <f t="shared" si="34"/>
         <v>15.451664025356576</v>
       </c>
       <c r="E20" s="1">
         <v>11656</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <f t="shared" ref="F20" si="39">(G20-E20)/E20*100</f>
         <v>-35.243651338366504</v>
       </c>
       <c r="G20" s="1">
         <v>7548</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="5">
         <f t="shared" ref="H20" si="40">(I20-G20)/G20*100</f>
         <v>47.734499205087438</v>
       </c>
@@ -1612,14 +1601,14 @@
         <f>40451-C20-E20-G20</f>
         <v>11151</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="5">
         <f>(K20-I20)/I20*100</f>
         <v>-13.846291812393508</v>
       </c>
       <c r="K20" s="1">
         <v>9607</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="5">
         <f>(M20-K20)/K20*100</f>
         <v>16.477568439679398</v>
       </c>
@@ -1628,13 +1617,13 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -1658,21 +1647,21 @@
       <c r="C23" s="1">
         <v>16192</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <f>(E23-C23)/C23*100</f>
         <v>-2.6185770750988144</v>
       </c>
       <c r="E23" s="1">
         <v>15768</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="5">
         <f>(G23-E23)/E23*100</f>
         <v>4.3759512937595124</v>
       </c>
       <c r="G23" s="1">
         <v>16458</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="5">
         <f>(I23-G23)/G23*100</f>
         <v>25.720014582573825</v>
       </c>
@@ -1680,14 +1669,14 @@
         <f>69109-C23-E23-G23</f>
         <v>20691</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="5">
         <f>(K23-I23)/I23*100</f>
         <v>-28.181334879899474</v>
       </c>
       <c r="K23" s="1">
         <v>14860</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="5">
         <f t="shared" ref="J23:L28" si="41">(M23-K23)/K23*100</f>
         <v>-2.0121130551816959</v>
       </c>
@@ -1702,21 +1691,21 @@
       <c r="C24" s="1">
         <v>1133</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="5">
         <f t="shared" ref="D24:D28" si="42">(E24-C24)/C24*100</f>
         <v>-12.444836716681378</v>
       </c>
       <c r="E24">
         <v>992</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="5">
         <f t="shared" ref="F24:F28" si="43">(G24-E24)/E24*100</f>
         <v>1.6129032258064515</v>
       </c>
       <c r="G24" s="1">
         <v>1008</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="5">
         <f t="shared" ref="H24:H28" si="44">(I24-G24)/G24*100</f>
         <v>-1.5873015873015872</v>
       </c>
@@ -1724,14 +1713,14 @@
         <f>4125-C24-E24-G24</f>
         <v>992</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="5">
         <f t="shared" si="41"/>
         <v>0.40322580645161288</v>
       </c>
       <c r="K24">
         <v>996</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="5">
         <f t="shared" ref="L24" si="45">(M24-K24)/K24*100</f>
         <v>-25.602409638554217</v>
       </c>
@@ -1746,21 +1735,21 @@
       <c r="C25" s="1">
         <v>19312</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <f t="shared" si="42"/>
         <v>5.6959403479701735E-2</v>
       </c>
       <c r="E25" s="1">
         <v>19323</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="5">
         <f t="shared" si="43"/>
         <v>-4.1401438699994825E-2</v>
       </c>
       <c r="G25" s="1">
         <v>19315</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="5">
         <f t="shared" si="44"/>
         <v>0.81283976184312701</v>
       </c>
@@ -1768,14 +1757,14 @@
         <f>77422-C25-E25-G25</f>
         <v>19472</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="5">
         <f t="shared" si="41"/>
         <v>0.21055875102711585</v>
       </c>
       <c r="K25" s="1">
         <v>19513</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="5">
         <f t="shared" ref="L25" si="46">(M25-K25)/K25*100</f>
         <v>0.1178701378568134</v>
       </c>
@@ -1790,21 +1779,21 @@
       <c r="C26" s="1">
         <v>6511</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <f t="shared" si="42"/>
         <v>4.6383044079250499</v>
       </c>
       <c r="E26" s="1">
         <v>6813</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="5">
         <f t="shared" si="43"/>
         <v>0.16145603992367533</v>
       </c>
       <c r="G26" s="1">
         <v>6824</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="5">
         <f t="shared" si="44"/>
         <v>-1.1283704572098476</v>
       </c>
@@ -1812,14 +1801,14 @@
         <f>26895-C26-E26-G26</f>
         <v>6747</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="5">
         <f t="shared" si="41"/>
         <v>-5.8544538313324441</v>
       </c>
       <c r="K26" s="1">
         <v>6352</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="5">
         <f t="shared" ref="L26" si="47">(M26-K26)/K26*100</f>
         <v>4.2034005037783375</v>
       </c>
@@ -1834,21 +1823,21 @@
       <c r="C27" s="1">
         <v>106918</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <f t="shared" si="42"/>
         <v>-140.21773695729439</v>
       </c>
       <c r="E27" s="1">
         <v>-43000</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="5">
         <f t="shared" si="43"/>
         <v>-26.451162790697673</v>
       </c>
       <c r="G27" s="1">
         <v>-31626</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="5">
         <f t="shared" si="44"/>
         <v>-398.57712009106427</v>
       </c>
@@ -1856,14 +1845,14 @@
         <f>126720-C27-E27-G27</f>
         <v>94428</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="5">
         <f t="shared" si="41"/>
         <v>97.988943957300805</v>
       </c>
       <c r="K27" s="1">
         <v>186957</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="5">
         <f t="shared" ref="L27" si="48">(M27-K27)/K27*100</f>
         <v>-175.95382895532128</v>
       </c>
@@ -1878,21 +1867,21 @@
       <c r="C28">
         <v>305</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="5">
         <f t="shared" si="42"/>
         <v>-15.081967213114755</v>
       </c>
       <c r="E28" s="1">
         <v>259</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="5">
         <f t="shared" si="43"/>
         <v>349.42084942084944</v>
       </c>
       <c r="G28" s="1">
         <v>1164</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="5">
         <f t="shared" si="44"/>
         <v>143.90034364261169</v>
       </c>
@@ -1900,14 +1889,14 @@
         <f>4567-C28-E28-G28</f>
         <v>2839</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="5">
         <f t="shared" si="41"/>
         <v>-98.414934836209937</v>
       </c>
       <c r="K28" s="1">
         <v>45</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="5">
         <f t="shared" ref="L28" si="49">(M28-K28)/K28*100</f>
         <v>16420</v>
       </c>
@@ -1916,13 +1905,13 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="D29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>29</v>
       </c>
@@ -1946,7 +1935,7 @@
       <c r="C31" s="1">
         <v>599803</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <f>(E31-C31)/C31*100</f>
         <v>25.500039179530614</v>
       </c>
@@ -1954,7 +1943,7 @@
         <f>1352556-C31</f>
         <v>752753</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="5">
         <f>(G31-E31)/E31*100</f>
         <v>-1.0988996390582302</v>
       </c>
@@ -1962,7 +1951,7 @@
         <f>2097037-E31-C31</f>
         <v>744481</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="5">
         <f>(I31-G31)/G31*100</f>
         <v>-16.155684295502503</v>
       </c>
@@ -1970,14 +1959,14 @@
         <f>2721242-C31-E31-G31</f>
         <v>624205</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="5">
         <f>(K31-I31)/I31*100</f>
         <v>-11.525059876162478</v>
       </c>
       <c r="K31" s="1">
         <v>552265</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="5">
         <f t="shared" ref="J31:L35" si="50">(M31-K31)/K31*100</f>
         <v>59.048282980091081</v>
       </c>
@@ -1993,7 +1982,7 @@
       <c r="C32" s="1">
         <v>543739</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <f t="shared" ref="D32:D35" si="51">(E32-C32)/C32*100</f>
         <v>13.034010802977164</v>
       </c>
@@ -2001,7 +1990,7 @@
         <f>1158349-C32</f>
         <v>614610</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="5">
         <f t="shared" ref="F32:F35" si="52">(G32-E32)/E32*100</f>
         <v>-5.7854574445583378</v>
       </c>
@@ -2009,7 +1998,7 @@
         <f>1737401-E32-C32</f>
         <v>579052</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="5">
         <f t="shared" ref="H32:H35" si="53">(I32-G32)/G32*100</f>
         <v>11.233015342318135</v>
       </c>
@@ -2017,14 +2006,14 @@
         <f>2381498-C32-E32-G32</f>
         <v>644097</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="5">
         <f t="shared" si="50"/>
         <v>-8.1102691054297722</v>
       </c>
       <c r="K32" s="1">
         <v>591859</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="5">
         <f t="shared" ref="L32" si="54">(M32-K32)/K32*100</f>
         <v>8.1167980887339723</v>
       </c>
@@ -2033,14 +2022,14 @@
         <v>639899</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="1">
         <v>-109160</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <f t="shared" si="51"/>
         <v>185.70355441553684</v>
       </c>
@@ -2048,7 +2037,7 @@
         <f>-421034-C33</f>
         <v>-311874</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="5">
         <f t="shared" si="52"/>
         <v>-22.541795725196714</v>
       </c>
@@ -2056,7 +2045,7 @@
         <f>-662606-C33-E33</f>
         <v>-241572</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="5">
         <f t="shared" si="53"/>
         <v>7.7008096964880037</v>
       </c>
@@ -2064,14 +2053,14 @@
         <f>-922781-C33-E33-G33</f>
         <v>-260175</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="5">
         <f t="shared" si="50"/>
         <v>48.200634188526955</v>
       </c>
       <c r="K33" s="1">
         <v>-385581</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="5">
         <f t="shared" ref="L33" si="55">(M33-K33)/K33*100</f>
         <v>-14.476595060441255</v>
       </c>
@@ -2080,14 +2069,14 @@
         <v>-329762</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="1">
         <v>-471781</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <f t="shared" si="51"/>
         <v>-6.4915713010909721</v>
       </c>
@@ -2095,7 +2084,7 @@
         <f>-912936-C34</f>
         <v>-441155</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="5">
         <f t="shared" si="52"/>
         <v>-25.357074044270156</v>
       </c>
@@ -2103,7 +2092,7 @@
         <f>-1242227-C34-E34</f>
         <v>-329291</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="5">
         <f t="shared" si="53"/>
         <v>-34.740396791895314</v>
       </c>
@@ -2111,14 +2100,14 @@
         <f>-1457121-C34-E34-G34</f>
         <v>-214894</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="5">
         <f t="shared" si="50"/>
         <v>84.631492735953543</v>
       </c>
       <c r="K34" s="1">
         <v>-396762</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="5">
         <f t="shared" ref="L34" si="56">(M34-K34)/K34*100</f>
         <v>3.7523754795066062</v>
       </c>
@@ -2127,14 +2116,14 @@
         <v>-411650</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" s="1">
         <v>-37256</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="5">
         <f t="shared" si="51"/>
         <v>270.83422804380501</v>
       </c>
@@ -2142,7 +2131,7 @@
         <f>-175414-C35</f>
         <v>-138158</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="5">
         <f t="shared" si="52"/>
         <v>-106.15744292766254</v>
       </c>
@@ -2150,7 +2139,7 @@
         <f>-166907-C35-E35</f>
         <v>8507</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="5">
         <f t="shared" si="53"/>
         <v>1885.9880098742212</v>
       </c>
@@ -2158,14 +2147,14 @@
         <f>2041-C35-E35-G35</f>
         <v>168948</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="5">
         <f t="shared" si="50"/>
         <v>-212.6370244098776</v>
       </c>
       <c r="K35" s="1">
         <v>-190298</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="5">
         <f t="shared" ref="L35" si="57">(M35-K35)/K35*100</f>
         <v>-46.749834470146823</v>
       </c>
@@ -2174,371 +2163,302 @@
         <v>-101334</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="D36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="L36" s="7"/>
-    </row>
-    <row r="37" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5" t="s">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="1">
         <v>601365</v>
       </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="6">
+      <c r="D38" s="5"/>
+      <c r="E38" s="1">
         <v>755987</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="6">
+      <c r="F38" s="5"/>
+      <c r="G38" s="1">
         <v>746942</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="6">
+      <c r="H38" s="5"/>
+      <c r="I38" s="1">
         <f>2730946-C38-E38-G38</f>
         <v>626652</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="6">
+      <c r="J38" s="5"/>
+      <c r="K38" s="1">
         <v>549809</v>
       </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="6">
+      <c r="L38" s="5"/>
+      <c r="M38" s="1">
         <v>883932</v>
       </c>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5" t="s">
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="1">
         <v>-204882</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="6">
+      <c r="D39" s="5"/>
+      <c r="E39" s="1">
         <v>-205777</v>
       </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="6">
+      <c r="F39" s="5"/>
+      <c r="G39" s="1">
         <v>-207317</v>
       </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="6">
+      <c r="H39" s="5"/>
+      <c r="I39" s="1">
         <f>-826097-C39-E39-G39</f>
         <v>-208121</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="6">
+      <c r="J39" s="5"/>
+      <c r="K39" s="1">
         <v>-209251</v>
       </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="6">
+      <c r="L39" s="5"/>
+      <c r="M39" s="1">
         <v>-213797</v>
       </c>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5" t="s">
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="1">
         <v>5293</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="6">
+      <c r="D40" s="5"/>
+      <c r="E40" s="1">
         <v>3926</v>
       </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="6">
+      <c r="F40" s="5"/>
+      <c r="G40" s="1">
         <v>2797</v>
       </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="6">
+      <c r="H40" s="5"/>
+      <c r="I40" s="1">
         <f>16095-C40-E40-G40</f>
         <v>4079</v>
       </c>
-      <c r="J40" s="7"/>
+      <c r="J40" s="5"/>
       <c r="K40" s="1">
         <v>3697</v>
       </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="6">
+      <c r="L40" s="5"/>
+      <c r="M40" s="1">
         <v>2293</v>
       </c>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A41" s="5"/>
-      <c r="B41" s="9" t="s">
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B41" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <f>C38-C39-C40</f>
         <v>800954</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="11">
+      <c r="D41" s="9"/>
+      <c r="E41" s="8">
         <f>E38-E39-E40</f>
         <v>957838</v>
       </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="11">
+      <c r="F41" s="9"/>
+      <c r="G41" s="8">
         <f>G38-G39-G40</f>
         <v>951462</v>
       </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="11">
+      <c r="H41" s="9"/>
+      <c r="I41" s="8">
         <f>I38-I39-I40</f>
         <v>830694</v>
       </c>
-      <c r="J41" s="12"/>
-      <c r="K41" s="11">
+      <c r="J41" s="9"/>
+      <c r="K41" s="8">
         <f>K38-K39-K40</f>
         <v>755363</v>
       </c>
-      <c r="L41" s="12"/>
-      <c r="M41" s="11">
+      <c r="L41" s="9"/>
+      <c r="M41" s="8">
         <f>M38-M39-M40</f>
         <v>1095436</v>
       </c>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5" t="s">
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="1">
         <v>-1562</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="6">
+      <c r="D43" s="5"/>
+      <c r="E43" s="1">
         <v>-3234</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6">
+      <c r="F43" s="5"/>
+      <c r="G43" s="1">
         <v>-2461</v>
       </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="6">
+      <c r="H43" s="5"/>
+      <c r="I43" s="1">
         <f>-9704-C43-E43-G43</f>
         <v>-2447</v>
       </c>
-      <c r="J43" s="7"/>
-      <c r="K43" s="6">
+      <c r="J43" s="5"/>
+      <c r="K43" s="1">
         <v>2456</v>
       </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="6">
+      <c r="L43" s="5"/>
+      <c r="M43" s="1">
         <v>-5564</v>
       </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5" t="s">
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44">
         <f>-C43/C38</f>
         <v>2.5974241932935904E-3</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="5">
+      <c r="D44" s="5"/>
+      <c r="E44">
         <f>-E43/E38</f>
         <v>4.2778513387134965E-3</v>
       </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="5">
+      <c r="F44" s="5"/>
+      <c r="G44">
         <f>-G43/G38</f>
         <v>3.2947671974530822E-3</v>
       </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="5">
+      <c r="H44" s="5"/>
+      <c r="I44">
         <f>-I43/I38</f>
         <v>3.9048786248188786E-3</v>
       </c>
-      <c r="J44" s="7"/>
-      <c r="K44" s="5">
+      <c r="J44" s="5"/>
+      <c r="K44">
         <f>-K43/K38</f>
         <v>-4.4670058147465753E-3</v>
       </c>
-      <c r="L44" s="7"/>
+      <c r="L44" s="5"/>
       <c r="M44" s="2">
         <v>-4.4669999999999996E-3</v>
       </c>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-    </row>
-    <row r="45" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="9" t="s">
+    </row>
+    <row r="45" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="13">
+      <c r="C45" s="6">
         <f>C41*(1-C44)</f>
         <v>798873.5827026848</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="13">
+      <c r="D45" s="9"/>
+      <c r="E45" s="6">
         <f>E41*(1-E44)</f>
         <v>953740.51142942929</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="13">
+      <c r="F45" s="9"/>
+      <c r="G45" s="6">
         <f>G41*(1-G44)</f>
         <v>948327.15421277692</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13">
+      <c r="H45" s="9"/>
+      <c r="I45" s="6">
         <f>I41*(1-I44)</f>
         <v>827450.24075563462</v>
       </c>
-      <c r="J45" s="12"/>
-      <c r="K45" s="13">
+      <c r="J45" s="9"/>
+      <c r="K45" s="6">
         <f>K41*(1-K44)</f>
         <v>758737.21091324452</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="13">
+      <c r="L45" s="9"/>
+      <c r="M45" s="6">
         <f>M41*(1-M44)</f>
         <v>1100329.3126119999</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="D46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B47" s="13" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B47" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="8">
         <f>C45+C24</f>
         <v>800006.5827026848</v>
       </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="14">
+      <c r="D47" s="9"/>
+      <c r="E47" s="8">
         <f>E45+E24</f>
         <v>954732.51142942929</v>
       </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="14">
+      <c r="F47" s="9"/>
+      <c r="G47" s="8">
         <f>G45+G24</f>
         <v>949335.15421277692</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="14">
+      <c r="H47" s="9"/>
+      <c r="I47" s="8">
         <f>I45+I24</f>
         <v>828442.24075563462</v>
       </c>
-      <c r="J47" s="12"/>
-      <c r="K47" s="14">
+      <c r="J47" s="9"/>
+      <c r="K47" s="8">
         <f>K45+K24</f>
         <v>759733.21091324452</v>
       </c>
-      <c r="L47" s="12"/>
-      <c r="M47" s="14">
+      <c r="L47" s="9"/>
+      <c r="M47" s="8">
         <f>M45+M24</f>
         <v>1101070.3126119999</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="D48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="L48" s="7"/>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
@@ -2547,71 +2467,71 @@
       <c r="C49" s="1">
         <v>-2410</v>
       </c>
-      <c r="D49" s="7"/>
+      <c r="D49" s="5"/>
       <c r="E49" s="1">
         <f>-5076-C49</f>
         <v>-2666</v>
       </c>
-      <c r="F49" s="7"/>
+      <c r="F49" s="5"/>
       <c r="G49" s="1">
         <f>-6442-E49-C49</f>
         <v>-1366</v>
       </c>
-      <c r="H49" s="7"/>
+      <c r="H49" s="5"/>
       <c r="I49" s="1">
         <f>-7526-G49-E49-C49</f>
         <v>-1084</v>
       </c>
-      <c r="J49" s="7"/>
+      <c r="J49" s="5"/>
       <c r="K49">
         <v>-156</v>
       </c>
-      <c r="L49" s="7"/>
+      <c r="L49" s="5"/>
       <c r="M49">
         <f>-828-K49</f>
         <v>-672</v>
       </c>
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="8">
         <f>C47+C49</f>
         <v>797596.5827026848</v>
       </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="14">
+      <c r="D50" s="9"/>
+      <c r="E50" s="8">
         <f>E47+E49</f>
         <v>952066.51142942929</v>
       </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="14">
+      <c r="F50" s="9"/>
+      <c r="G50" s="8">
         <f>G47+G49</f>
         <v>947969.15421277692</v>
       </c>
-      <c r="H50" s="12"/>
-      <c r="I50" s="14">
+      <c r="H50" s="9"/>
+      <c r="I50" s="8">
         <f>I47+I49</f>
         <v>827358.24075563462</v>
       </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="14">
+      <c r="J50" s="9"/>
+      <c r="K50" s="8">
         <f>K47+K49</f>
         <v>759577.21091324452</v>
       </c>
-      <c r="L50" s="12"/>
-      <c r="M50" s="14">
+      <c r="L50" s="9"/>
+      <c r="M50" s="8">
         <f>M47+M49</f>
         <v>1100398.3126119999</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="L51" s="7"/>
+      <c r="D51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="L51" s="5"/>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
@@ -2620,26 +2540,26 @@
       <c r="C52" s="1">
         <v>-5026</v>
       </c>
-      <c r="D52" s="7"/>
+      <c r="D52" s="5"/>
       <c r="E52" s="1">
         <f>-20005-C52</f>
         <v>-14979</v>
       </c>
-      <c r="F52" s="7"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="1">
         <f>-5910-E52-C52</f>
         <v>14095</v>
       </c>
-      <c r="H52" s="7"/>
+      <c r="H52" s="5"/>
       <c r="I52" s="1">
         <f>3736-G52-E52-C52</f>
         <v>9646</v>
       </c>
-      <c r="J52" s="7"/>
+      <c r="J52" s="5"/>
       <c r="K52" s="1">
         <v>-6666</v>
       </c>
-      <c r="L52" s="7"/>
+      <c r="L52" s="5"/>
       <c r="M52" s="1">
         <f>-6247-K52</f>
         <v>419</v>
@@ -2652,26 +2572,26 @@
       <c r="C53" s="1">
         <v>-39510</v>
       </c>
-      <c r="D53" s="7"/>
+      <c r="D53" s="5"/>
       <c r="E53" s="1">
         <f>-10670-C53</f>
         <v>28840</v>
       </c>
-      <c r="F53" s="7"/>
+      <c r="F53" s="5"/>
       <c r="G53" s="1">
         <f>-39573-E53-C53</f>
         <v>-28903</v>
       </c>
-      <c r="H53" s="7"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="1">
         <f>-13443-G53-E53-C53</f>
         <v>26130</v>
       </c>
-      <c r="J53" s="7"/>
+      <c r="J53" s="5"/>
       <c r="K53" s="1">
         <v>-22898</v>
       </c>
-      <c r="L53" s="7"/>
+      <c r="L53" s="5"/>
       <c r="M53" s="1">
         <f>2610-K53</f>
         <v>25508</v>
@@ -2684,124 +2604,124 @@
       <c r="C54" s="1">
         <v>-1524</v>
       </c>
-      <c r="D54" s="7"/>
+      <c r="D54" s="5"/>
       <c r="E54" s="1">
         <f>3125-C54</f>
         <v>4649</v>
       </c>
-      <c r="F54" s="7"/>
+      <c r="F54" s="5"/>
       <c r="G54" s="1">
         <f>-178-E54-C54</f>
         <v>-3303</v>
       </c>
-      <c r="H54" s="7"/>
+      <c r="H54" s="5"/>
       <c r="I54" s="1">
         <f>-1505-G54-E54-C54</f>
         <v>-1327</v>
       </c>
-      <c r="J54" s="7"/>
+      <c r="J54" s="5"/>
       <c r="K54">
         <v>83</v>
       </c>
-      <c r="L54" s="7"/>
+      <c r="L54" s="5"/>
       <c r="M54" s="1">
         <f>-2305-K54</f>
         <v>-2388</v>
       </c>
     </row>
-    <row r="55" spans="2:13" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="13" t="s">
+    <row r="55" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="8">
         <f>C52+C53+C54</f>
         <v>-46060</v>
       </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="14">
+      <c r="D55" s="9"/>
+      <c r="E55" s="8">
         <f>E52+E53+E54</f>
         <v>18510</v>
       </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="14">
+      <c r="F55" s="9"/>
+      <c r="G55" s="8">
         <f>G52+G53+G54</f>
         <v>-18111</v>
       </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="14">
+      <c r="H55" s="9"/>
+      <c r="I55" s="8">
         <f>I52+I53+I54</f>
         <v>34449</v>
       </c>
-      <c r="J55" s="12"/>
-      <c r="K55" s="14">
+      <c r="J55" s="9"/>
+      <c r="K55" s="8">
         <f>K52+K53+K54</f>
         <v>-29481</v>
       </c>
-      <c r="L55" s="12"/>
-      <c r="M55" s="14">
+      <c r="L55" s="9"/>
+      <c r="M55" s="8">
         <f>M52+M53+M54</f>
         <v>23539</v>
       </c>
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="L56" s="7"/>
-    </row>
-    <row r="57" spans="2:13" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="13" t="s">
+      <c r="D56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C57" s="14">
+      <c r="C57" s="8">
         <f>C50+C55</f>
         <v>751536.5827026848</v>
       </c>
-      <c r="D57" s="12"/>
-      <c r="E57" s="14">
+      <c r="D57" s="9"/>
+      <c r="E57" s="8">
         <f>E50+E55</f>
         <v>970576.51142942929</v>
       </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="14">
+      <c r="F57" s="9"/>
+      <c r="G57" s="8">
         <f>G50+G55</f>
         <v>929858.15421277692</v>
       </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="14">
+      <c r="H57" s="9"/>
+      <c r="I57" s="8">
         <f>I50+I55</f>
         <v>861807.24075563462</v>
       </c>
-      <c r="J57" s="12"/>
-      <c r="K57" s="14">
+      <c r="J57" s="9"/>
+      <c r="K57" s="8">
         <f>K50+K55</f>
         <v>730096.21091324452</v>
       </c>
-      <c r="L57" s="12"/>
-      <c r="M57" s="14">
+      <c r="L57" s="9"/>
+      <c r="M57" s="8">
         <f>M50+M55</f>
         <v>1123937.3126119999</v>
       </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B60" s="13"/>
+      <c r="B60" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>-5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>-5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2813,19 +2733,19 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
       <formula>-5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="lessThan">
       <formula>-5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2864,12 +2784,12 @@
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="8">
         <f>'Balance Sheet'!C57</f>
         <v>751536.5827026848</v>
       </c>
       <c r="D2">
-        <f>LOG(C2)</f>
+        <f t="shared" ref="D2:D7" si="0">LOG(C2)</f>
         <v>5.8759501256803714</v>
       </c>
       <c r="F2" cm="1">
@@ -2887,12 +2807,12 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="8">
         <f>'Balance Sheet'!E57</f>
         <v>970576.51142942929</v>
       </c>
       <c r="D3">
-        <f>LOG(C3)</f>
+        <f t="shared" si="0"/>
         <v>5.9870297769030039</v>
       </c>
       <c r="F3">
@@ -2909,12 +2829,12 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="8">
         <f>'Balance Sheet'!G57</f>
         <v>929858.15421277692</v>
       </c>
       <c r="D4">
-        <f>LOG(C4)</f>
+        <f t="shared" si="0"/>
         <v>5.9684167038861338</v>
       </c>
       <c r="F4">
@@ -2931,12 +2851,12 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="8">
         <f>'Balance Sheet'!I57</f>
         <v>861807.24075563462</v>
       </c>
       <c r="D5">
-        <f>LOG(C5)</f>
+        <f t="shared" si="0"/>
         <v>5.9354101386349276</v>
       </c>
       <c r="F5">
@@ -2953,12 +2873,12 @@
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="8">
         <f>'Balance Sheet'!K57</f>
         <v>730096.21091324452</v>
       </c>
       <c r="D6">
-        <f>LOG(C6)</f>
+        <f t="shared" si="0"/>
         <v>5.863380094525243</v>
       </c>
       <c r="F6">
@@ -2975,12 +2895,12 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="8">
         <f>'Balance Sheet'!M57</f>
         <v>1123937.3126119999</v>
       </c>
       <c r="D7">
-        <f>LOG(C7)</f>
+        <f t="shared" si="0"/>
         <v>6.0507420892171098</v>
       </c>
     </row>
@@ -2993,11 +2913,11 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
       <c r="F9">
         <f>EXP(F2)-1</f>
         <v>1.3519261416133244E-2</v>
@@ -3008,17 +2928,17 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
       <c r="F10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
       <c r="F11">
         <f>POWER(1+F9,4)-1</f>
         <v>5.5183585329837026E-2</v>
@@ -3095,14 +3015,14 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="17">
+      <c r="B17" s="10">
         <v>2028</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="10">
         <f>(1+G9)*C16</f>
         <v>4283165.7321446696</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="10">
         <f>(1+G9)*D16</f>
         <v>4533726.9077882692</v>
       </c>
@@ -3142,100 +3062,98 @@
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="15"/>
+      <c r="C21" s="11"/>
       <c r="D21">
         <f>(C17*(1+0.025))/(0.075-0.025)</f>
         <v>87804897.508965716</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17">
+      <c r="C22" s="12"/>
+      <c r="D22" s="10">
         <f>(C17*(1+0.03))/(0.075-0.03)</f>
         <v>98036904.535755783</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="15"/>
+      <c r="C23" s="11"/>
       <c r="D23">
         <f>(C17*(1+0.015))/(0.075-0.015)</f>
         <v>72456886.968780652</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="15"/>
+      <c r="C25" s="11"/>
       <c r="D25">
         <f>(C17*(1+0.025))/(0.085-0.025)</f>
         <v>73170747.924138084</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="17">
+      <c r="C26" s="12"/>
+      <c r="D26" s="10">
         <f>(C17*(1+0.03))/(0.085-0.03)</f>
         <v>80212012.801982</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="15"/>
+      <c r="C27" s="11"/>
       <c r="D27">
         <f>(C17*(1+0.015))/(0.085-0.015)</f>
         <v>62105903.116097696</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="15"/>
+      <c r="C29" s="11"/>
       <c r="D29">
         <f>(C17*(1+0.025))/(0.065-0.025)</f>
         <v>109756121.88620713</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="17">
+      <c r="C30" s="12"/>
+      <c r="D30" s="10">
         <f>(C17*(1+0.03))/(0.065-0.03)</f>
         <v>126047448.68882886</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="15"/>
+      <c r="C31" s="11"/>
       <c r="D31">
         <f>(C17*(1+0.015))/(0.065-0.015)</f>
         <v>86948264.362536773</v>
@@ -3243,6 +3161,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B9:D11"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
@@ -3250,11 +3173,6 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B9:D11"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3307,7 +3225,7 @@
       <c r="B4">
         <v>2025</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="1">
         <f>'DCF Calculations'!C14</f>
         <v>3645698.918493656</v>
       </c>
@@ -3343,7 +3261,7 @@
       <c r="B5">
         <v>2026</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <f>'DCF Calculations'!C15</f>
         <v>3846881.6558492454</v>
       </c>
@@ -3379,7 +3297,7 @@
       <c r="B6">
         <v>2027</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <f>'DCF Calculations'!C16</f>
         <v>4059166.3779585869</v>
       </c>
@@ -3415,7 +3333,7 @@
       <c r="B7">
         <v>2028</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <f>'DCF Calculations'!C17</f>
         <v>4283165.7321446696</v>
       </c>

--- a/YSIG/Stock Pitch/VICI/10q/VICI Over Time.xlsx
+++ b/YSIG/Stock Pitch/VICI/10q/VICI Over Time.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Documents/Notes/YSIG/Stock Pitch/VICI/10q/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6210C1-22AC-CE49-BB85-1B4ABB857129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F85F00-AC6B-414C-AAE8-227E4AAED0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" activeTab="2" xr2:uid="{E4D61E25-3F2C-2549-A6B3-A831DB9DF31D}"/>
   </bookViews>
@@ -446,13 +446,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2913,11 +2913,11 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
       <c r="F9">
         <f>EXP(F2)-1</f>
         <v>1.3519261416133244E-2</v>
@@ -2928,17 +2928,17 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
       <c r="F10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
       <c r="F11">
         <f>POWER(1+F9,4)-1</f>
         <v>5.5183585329837026E-2</v>
@@ -3062,98 +3062,98 @@
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="11"/>
+      <c r="C21" s="12"/>
       <c r="D21">
         <f>(C17*(1+0.025))/(0.075-0.025)</f>
         <v>87804897.508965716</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="12"/>
+      <c r="C22" s="13"/>
       <c r="D22" s="10">
         <f>(C17*(1+0.03))/(0.075-0.03)</f>
         <v>98036904.535755783</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="11"/>
+      <c r="C23" s="12"/>
       <c r="D23">
         <f>(C17*(1+0.015))/(0.075-0.015)</f>
         <v>72456886.968780652</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="11"/>
+      <c r="C25" s="12"/>
       <c r="D25">
         <f>(C17*(1+0.025))/(0.085-0.025)</f>
         <v>73170747.924138084</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="12"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="10">
         <f>(C17*(1+0.03))/(0.085-0.03)</f>
         <v>80212012.801982</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="11"/>
+      <c r="C27" s="12"/>
       <c r="D27">
         <f>(C17*(1+0.015))/(0.085-0.015)</f>
         <v>62105903.116097696</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="11"/>
+      <c r="C29" s="12"/>
       <c r="D29">
         <f>(C17*(1+0.025))/(0.065-0.025)</f>
         <v>109756121.88620713</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="12"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="10">
         <f>(C17*(1+0.03))/(0.065-0.03)</f>
         <v>126047448.68882886</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="11"/>
+      <c r="C31" s="12"/>
       <c r="D31">
         <f>(C17*(1+0.015))/(0.065-0.015)</f>
         <v>86948264.362536773</v>
@@ -3161,11 +3161,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B9:D11"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
@@ -3173,6 +3168,11 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B9:D11"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
